--- a/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
+++ b/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\src\main\java\org\dsa\journeywithpravallika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F318FF9-CD45-4C56-8524-A19C067E45E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B5A108-B68E-4FC2-BCBD-8D177C929D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2790" yWindow="2310" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="2710" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -103,6 +103,30 @@
   </si>
   <si>
     <t>https://www.instagram.com/reel/DZpti5Bzc2p/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZuxE-KzsBo/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Two Sum Sorted Array</t>
+  </si>
+  <si>
+    <t>Container with water</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZxV8-jTa4L/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>3 Sum unique triplet</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZz1uQPzdui/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Trapping rain water</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZ5HAaUTv_Q/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
   </si>
 </sst>
 </file>
@@ -126,12 +150,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -146,9 +176,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6809B420-3370-4819-A184-932D095C9ED8}">
-  <dimension ref="A2:D9"/>
+  <dimension ref="A2:F14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.453125" customWidth="1"/>
@@ -437,7 +468,7 @@
     <col min="4" max="4" width="50.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,7 +482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -465,7 +496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -479,7 +510,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -493,7 +524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -507,7 +538,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -521,7 +552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -535,7 +566,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -547,6 +578,70 @@
       </c>
       <c r="D9" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
+++ b/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\src\main\java\org\dsa\journeywithpravallika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/src/main/java/org/dsa/journeywithpravallika/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B5A108-B68E-4FC2-BCBD-8D177C929D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABCE7AD6-6F50-46F0-9AB0-66EDA8850724}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="2710" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="1820" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -126,7 +126,25 @@
     <t>Trapping rain water</t>
   </si>
   <si>
+    <t>Leetcode Link</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/trapping-rain-water/description/</t>
+  </si>
+  <si>
     <t>https://www.instagram.com/reel/DZ5HAaUTv_Q/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Put in leetcode</t>
+  </si>
+  <si>
+    <t>Sliding Window</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DZ-PGUpzK4P/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Longest substring without repeating characters</t>
   </si>
 </sst>
 </file>
@@ -195,6 +213,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -460,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6809B420-3370-4819-A184-932D095C9ED8}">
-  <dimension ref="A2:F14"/>
+  <dimension ref="A2:G18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.453125" customWidth="1"/>
@@ -468,7 +490,7 @@
     <col min="4" max="4" width="50.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,8 +503,11 @@
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -496,7 +521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -510,7 +535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -524,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -538,7 +563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -552,7 +577,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -566,7 +591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -580,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -594,7 +619,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -608,7 +633,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -622,7 +647,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -630,7 +655,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
@@ -641,10 +666,46 @@
         <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
+++ b/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/src/main/java/org/dsa/journeywithpravallika/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABCE7AD6-6F50-46F0-9AB0-66EDA8850724}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10622C1A-BD8B-442D-838B-21DBA2F71411}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="1820" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4800" yWindow="1820" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -145,6 +145,24 @@
   </si>
   <si>
     <t>Longest substring without repeating characters</t>
+  </si>
+  <si>
+    <t>Count of Longest repeating same char by replaceing k count</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaLHpxYTWgU/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/longest-repeating-character-replacement/description/</t>
+  </si>
+  <si>
+    <t>Minimum Size subarray sum</t>
+  </si>
+  <si>
+    <t>Good Ques</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/alphaintern.in?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
   </si>
 </sst>
 </file>
@@ -482,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6809B420-3370-4819-A184-932D095C9ED8}">
-  <dimension ref="A2:G18"/>
+  <dimension ref="A2:G28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.453125" customWidth="1"/>
@@ -693,15 +711,51 @@
       <c r="A16">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
+++ b/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/src/main/java/org/dsa/journeywithpravallika/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10622C1A-BD8B-442D-838B-21DBA2F71411}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11A7AFD3-6FB5-410F-9629-E900DA593DD0}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="1820" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="2900" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -159,10 +159,28 @@
     <t>Minimum Size subarray sum</t>
   </si>
   <si>
+    <t>https://www.instagram.com/reel/DaNbhQlz75R/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
     <t>Good Ques</t>
   </si>
   <si>
     <t>https://www.instagram.com/alphaintern.in?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+  </si>
+  <si>
+    <t>Max Sum subarray of size k</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaQQP0yTQlP/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Find all anagram indices</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaVdbQlTOU3/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Optimal Need to do</t>
   </si>
 </sst>
 </file>
@@ -724,7 +742,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>13</v>
       </c>
@@ -734,28 +752,52 @@
       <c r="C17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
+++ b/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/src/main/java/org/dsa/journeywithpravallika/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11A7AFD3-6FB5-410F-9629-E900DA593DD0}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C5DDE62-C37A-4345-A9EB-835AC5D525ED}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="2900" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2900" yWindow="3400" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -181,6 +181,21 @@
   </si>
   <si>
     <t>Optimal Need to do</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/Daabf_YT9gJ/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Fruits into basket</t>
+  </si>
+  <si>
+    <t>Minimum window substring</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/Dafq0bbTgYt/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/minimum-window-substring/description/</t>
   </si>
 </sst>
 </file>
@@ -780,7 +795,7 @@
       <c r="C19" t="s">
         <v>46</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E19" t="s">
@@ -790,6 +805,32 @@
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">

--- a/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
+++ b/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/src/main/java/org/dsa/journeywithpravallika/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C5DDE62-C37A-4345-A9EB-835AC5D525ED}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02FC70E7-AA89-44D6-9484-F361EE6E47F6}"/>
   <bookViews>
-    <workbookView xWindow="2900" yWindow="3400" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -196,6 +196,15 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/minimum-window-substring/description/</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Stack Intro</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DaiLp9GTabm/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
   </si>
 </sst>
 </file>
@@ -833,6 +842,30 @@
         <v>53</v>
       </c>
     </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>20</v>
+      </c>
+    </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>42</v>

--- a/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
+++ b/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce4bfbb34b637776/Desktop/Data/Upskill_OnlineCourse/DSA_Cohort_Pradeep/DSA_Cohort/src/main/java/org/dsa/journeywithpravallika/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\src\main\java\org\dsa\journeywithpravallika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{D9A73912-350E-47A6-B764-DC5424942A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02FC70E7-AA89-44D6-9484-F361EE6E47F6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D811E2B5-4159-4BA1-9381-B966B05EE516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2750" yWindow="3910" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
   <si>
     <t xml:space="preserve">Day </t>
   </si>
@@ -205,6 +205,18 @@
   </si>
   <si>
     <t>https://www.instagram.com/reel/DaiLp9GTabm/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Valid Parentheses</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/Dakw0OhTwPF/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>Next Largest on right</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/reel/DapiQnkT3UV/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
   </si>
 </sst>
 </file>
@@ -273,10 +285,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -860,11 +868,36 @@
       <c r="A23">
         <v>19</v>
       </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>20</v>
       </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B28" t="s">

--- a/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
+++ b/src/main/java/org/dsa/journeywithpravallika/dayWiseSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shrey\OneDrive\Desktop\Data\Upskill_OnlineCourse\DSA_Cohort_Pradeep\DSA_Cohort\src\main\java\org\dsa\journeywithpravallika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D811E2B5-4159-4BA1-9381-B966B05EE516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AB7BD2-754C-41EA-888C-5649ACE973F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2750" yWindow="3910" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2750" yWindow="1820" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -550,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6809B420-3370-4819-A184-932D095C9ED8}">
-  <dimension ref="A2:G28"/>
+  <dimension ref="A2:G33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.453125" customWidth="1"/>
@@ -899,11 +899,46 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>22</v>
+      </c>
+    </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
+      <c r="A28">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
         <v>42</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C33" t="s">
         <v>43</v>
       </c>
     </row>
